--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xdrtas\sources\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DACF0C-E6D1-403B-A48D-03B483E33508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E257FD-DC28-4D85-AF8F-F791460603A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-102" yWindow="1488" windowWidth="18372" windowHeight="10296" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -509,7 +509,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -962,7 +962,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -978,7 +978,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1320,32 +1320,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D423364-12D3-4C3A-8A6B-C3645EBFE927}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.15625" style="1"/>
-    <col min="18" max="18" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.25" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="14.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.125" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15.75" thickBot="1">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15.75" thickBot="1">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1452,9 +1452,12 @@
         <f>AND(L3,M3)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="32"/>
-    </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q3" s="32" t="str">
+        <f>IF(P3,"GOAL MET", "NOT MET")</f>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="15.75" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1511,9 +1514,12 @@
         <f t="shared" ref="P4:P12" si="10">AND(L4,M4)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="32"/>
-    </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q4" s="32" t="str">
+        <f t="shared" ref="Q4:Q12" si="11">IF(P4,"GOAL MET", "NOT MET")</f>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="15.75" thickBot="1">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1570,9 +1576,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="32"/>
-    </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q5" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="15.75" thickBot="1">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1629,9 +1638,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="32"/>
-    </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q6" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="15.75" thickBot="1">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1688,9 +1700,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="32"/>
-    </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q7" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="15.75" thickBot="1">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1747,9 +1762,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="32"/>
-    </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q8" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="15.75" thickBot="1">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1806,9 +1824,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="32"/>
-    </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q9" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="15.75" thickBot="1">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1865,9 +1886,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="32"/>
-    </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q10" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="15.75" thickBot="1">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1924,9 +1948,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="32"/>
-    </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q11" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="15.75" thickBot="1">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -1983,14 +2010,17 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q12" s="33"/>
-    </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q12" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="15.75" thickBot="1">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1998,7 +2028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15.75" thickBot="1">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2014,33 +2044,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C913A13C-1EE0-4C25-B641-D7D4D62C7E1E}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.41796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.15625" style="1"/>
-    <col min="19" max="19" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.25" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.375" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.125" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.625" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9.625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.125" style="1"/>
+    <col min="19" max="19" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15.75" thickBot="1">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2090,7 +2120,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15.75" thickBot="1">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2152,7 +2182,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:17" ht="15.75" thickBot="1">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2214,7 +2244,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:17" ht="15.75" thickBot="1">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -2276,7 +2306,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:17" ht="15.75" thickBot="1">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2368,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:17" ht="15.75" thickBot="1">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -2400,7 +2430,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:17" ht="15.75" thickBot="1">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -2462,7 +2492,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:17" ht="15.75" thickBot="1">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2554,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:17" ht="15.75" thickBot="1">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -2586,7 +2616,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:17" ht="15.75" thickBot="1">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2678,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:17" ht="15.75" thickBot="1">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -2710,12 +2740,12 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:17" ht="15.75" thickBot="1">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -2723,7 +2753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15.75" thickBot="1">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2739,29 +2769,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18E6D21-2229-4383-8B9A-431F68FAE08C}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.15625" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.9453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.3125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="68.125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="14.25" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.75" customWidth="1"/>
+    <col min="18" max="18" width="12.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="15">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -2817,7 +2847,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -2848,8 +2878,40 @@
       <c r="J2" s="27" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K2" t="str">
+        <f>IF($A2=K$1,"Role Desire","Not Desire")</f>
+        <v>Not Desire</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF($A2=L$1,"Role Desire","Not Desire")</f>
+        <v>Not Desire</v>
+      </c>
+      <c r="M2" t="str">
+        <f>IF($A2=K$1,"Role Desire",IF($A2=L$1,"Role Desire","Not Desire"))</f>
+        <v>Not Desire</v>
+      </c>
+      <c r="N2" t="b">
+        <f>IF($A2=K$1,$A2=$L$1)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <f>OR($A2=K$1,$A2=$L$1)</f>
+        <v>0</v>
+      </c>
+      <c r="P2" t="str">
+        <f>IF(OR($A2=$K$1,$A2=$L$1),"Role Desired","NOT Desired")</f>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>IF($H2&gt;$Q$1,"Salary &gt; "&amp;$Q$1,"Salary Low")</f>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R2" t="str" cm="1">
+        <f t="array" ref="R2">_xlfn.IFS($H2="","No Data",$H2&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -2880,8 +2942,40 @@
       <c r="J3" s="27" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:L21" si="0">IF($A3=K$1,"Role Desire","Not Desire")</f>
+        <v>Role Desire</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M21" si="1">IF($A3=K$1,"Role Desire",IF($A3=L$1,"Role Desire","Not Desire"))</f>
+        <v>Role Desire</v>
+      </c>
+      <c r="N3" t="b">
+        <f t="shared" ref="N3:N21" si="2">IF($A3=K$1,$A3=$L$1)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" t="b">
+        <f t="shared" ref="O3:O21" si="3">OR($A3=K$1,$A3=$L$1)</f>
+        <v>1</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P21" si="4">IF(OR($A3=$K$1,$A3=$L$1),"Role Desired","NOT Desired")</f>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q21" si="5">IF($H3&gt;$Q$1,"Salary &gt; "&amp;$Q$1,"Salary Low")</f>
+        <v>Salary Low</v>
+      </c>
+      <c r="R3" t="str" cm="1">
+        <f t="array" ref="R3">_xlfn.IFS($H3="","No Data",$H3&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary Low</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -2910,8 +3004,40 @@
       <c r="J4" s="27" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K4" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O4" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R4" t="str" cm="1">
+        <f t="array" ref="R4">_xlfn.IFS($H4="","No Data",$H4&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -2940,8 +3066,40 @@
       <c r="J5" s="27" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K5" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N5" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R5" t="str" cm="1">
+        <f t="array" ref="R5">_xlfn.IFS($H5="","No Data",$H5&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -2970,8 +3128,40 @@
       <c r="J6" s="27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K6" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R6" t="str" cm="1">
+        <f t="array" ref="R6">_xlfn.IFS($H6="","No Data",$H6&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -3000,8 +3190,40 @@
       <c r="J7" s="27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N7" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R7" t="str" cm="1">
+        <f t="array" ref="R7">_xlfn.IFS($H7="","No Data",$H7&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -3030,8 +3252,40 @@
       <c r="J8" s="27" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N8" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R8" t="str" cm="1">
+        <f t="array" ref="R8">_xlfn.IFS($H8="","No Data",$H8&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -3062,8 +3316,40 @@
       <c r="J9" s="27" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N9" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O9" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R9" t="str" cm="1">
+        <f t="array" ref="R9">_xlfn.IFS($H9="","No Data",$H9&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -3092,8 +3378,40 @@
       <c r="J10" s="27" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N10" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O10" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R10" t="str" cm="1">
+        <f t="array" ref="R10">_xlfn.IFS($H10="","No Data",$H10&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -3124,8 +3442,40 @@
       <c r="J11" s="27" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N11" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R11" t="str" cm="1">
+        <f t="array" ref="R11">_xlfn.IFS($H11="","No Data",$H11&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -3156,8 +3506,40 @@
       <c r="J12" s="27" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N12" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R12" t="str" cm="1">
+        <f t="array" ref="R12">_xlfn.IFS($H12="","No Data",$H12&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -3188,8 +3570,40 @@
       <c r="J13" s="27" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N13" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O13" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R13" t="str" cm="1">
+        <f t="array" ref="R13">_xlfn.IFS($H13="","No Data",$H13&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -3220,8 +3634,40 @@
       <c r="J14" s="27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K14" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N14" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R14" t="str" cm="1">
+        <f t="array" ref="R14">_xlfn.IFS($H14="","No Data",$H14&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -3252,8 +3698,40 @@
       <c r="J15" s="27" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K15" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N15" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O15" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R15" t="str" cm="1">
+        <f t="array" ref="R15">_xlfn.IFS($H15="","No Data",$H15&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary Low</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
@@ -3284,8 +3762,40 @@
       <c r="J16" s="27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N16" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R16" t="str" cm="1">
+        <f t="array" ref="R16">_xlfn.IFS($H16="","No Data",$H16&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -3316,8 +3826,40 @@
       <c r="J17" s="27" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K17" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N17" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O17" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R17" t="str" cm="1">
+        <f t="array" ref="R17">_xlfn.IFS($H17="","No Data",$H17&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -3346,8 +3888,40 @@
       <c r="J18" s="27" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K18" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N18" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O18" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R18" t="str" cm="1">
+        <f t="array" ref="R18">_xlfn.IFS($H18="","No Data",$H18&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -3378,8 +3952,40 @@
       <c r="J19" s="27" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K19" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N19" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q19" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R19" t="str" cm="1">
+        <f t="array" ref="R19">_xlfn.IFS($H19="","No Data",$H19&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -3408,8 +4014,40 @@
       <c r="J20" s="27" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K20" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="N20" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="4"/>
+        <v>NOT Desired</v>
+      </c>
+      <c r="Q20" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary Low</v>
+      </c>
+      <c r="R20" t="str" cm="1">
+        <f t="array" ref="R20">_xlfn.IFS($H20="","No Data",$H20&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>No Data</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -3440,38 +4078,71 @@
       <c r="J21" s="27" t="s">
         <v>135</v>
       </c>
+      <c r="K21" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Desire</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="0"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="1"/>
+        <v>Role Desire</v>
+      </c>
+      <c r="N21" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P21" t="str">
+        <f t="shared" si="4"/>
+        <v>Role Desired</v>
+      </c>
+      <c r="Q21" t="str">
+        <f t="shared" si="5"/>
+        <v>Salary &gt; 85000</v>
+      </c>
+      <c r="R21" t="str" cm="1">
+        <f t="array" ref="R21">_xlfn.IFS($H21="","No Data",$H21&gt;=$Q$1,"Salary &gt;"&amp;$Q$1,TRUE,"Salary Low")</f>
+        <v>Salary &gt;85000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4064259-8981-41EE-A951-64D7FCDC9F77}">
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.83984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.41796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18 16384:16384" ht="15">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -3531,7 +4202,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18 16384:16384">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -3595,7 +4266,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18 16384:16384">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -3659,7 +4330,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18 16384:16384">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -3721,7 +4392,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18 16384:16384">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -3783,7 +4454,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18 16384:16384">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -3845,7 +4516,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18 16384:16384">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -3907,7 +4578,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18 16384:16384">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -3969,7 +4640,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18 16384:16384">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -4033,7 +4704,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18 16384:16384">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -4095,7 +4766,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18 16384:16384">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -4159,7 +4830,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18 16384:16384">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -4223,7 +4894,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18 16384:16384">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -4287,7 +4958,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18 16384:16384">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -4351,7 +5022,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18 16384:16384">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -4415,7 +5086,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18 16384:16384">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
@@ -4479,7 +5150,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -4543,7 +5214,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -4605,7 +5276,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -4669,7 +5340,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -4731,7 +5402,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -4804,17 +5475,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EBE098-CD97-45AE-AE7E-86DF2D94E426}">
   <dimension ref="B2:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="6.578125" customWidth="1"/>
-    <col min="2" max="2" width="13.41796875" customWidth="1"/>
-    <col min="3" max="3" width="31.41796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.625" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:6" ht="15">
       <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
@@ -4831,7 +5502,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:6">
       <c r="B3" s="27" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
@@ -4851,7 +5522,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:6">
       <c r="B4" s="27" t="e">
         <f>A4 + "text"</f>
         <v>#VALUE!</v>
@@ -4871,7 +5542,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:6">
       <c r="B5" s="12" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -4891,7 +5562,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:6">
       <c r="B6" s="12" t="e" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">COUNTT(A3:A9)</f>
         <v>#NAME?</v>
@@ -4911,7 +5582,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:6">
       <c r="B7" s="27" t="e">
         <f>VLOOKUP("Value", A1:A10, 2, FALSE)</f>
         <v>#N/A</v>
@@ -4931,7 +5602,7 @@
         <v>This hides #N/A error</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:6">
       <c r="B8" s="27" t="e">
         <f>SQRT(-1)</f>
         <v>#NUM!</v>
@@ -4951,7 +5622,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:6">
       <c r="B9" s="27" t="e">
         <f>SUM(A1:A10 C1:C10)</f>
         <v>#NULL!</v>
@@ -4979,14 +5650,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B83CC08-3BAC-45FD-A105-07186D54808A}">
   <dimension ref="B1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.578125" customWidth="1"/>
+    <col min="2" max="2" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:5" ht="15" thickBot="1"/>
+    <row r="2" spans="2:5" ht="15">
       <c r="B2" s="36" t="s">
         <v>137</v>
       </c>
@@ -5000,7 +5671,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:5">
       <c r="B3" s="38" t="b">
         <v>1</v>
       </c>
@@ -5016,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:5">
       <c r="B4" s="38" t="b">
         <v>1</v>
       </c>
@@ -5032,7 +5703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:5">
       <c r="B5" s="38" t="b">
         <v>0</v>
       </c>
@@ -5048,7 +5719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:5" ht="15" thickBot="1">
       <c r="B6" s="40" t="b">
         <v>0</v>
       </c>
